--- a/samples/2020-09-24-hazira-gas-release-fire/outputs/nine-m-analysis.actions-template.xlsx
+++ b/samples/2020-09-24-hazira-gas-release-fire/outputs/nine-m-analysis.actions-template.xlsx
@@ -821,7 +821,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter>
     <oddHeader>&amp;CLearning purposes: not a statutory document · DRAFT</oddHeader>
-    <oddFooter>&amp;CGenerated with ProbeMatrix Learnings Coach v2.0.0a6 (open source, MIT) from a ProbeMatrix four-level human-factors investigation. ProbeMatrix by Eyekyam: ashley@eyekyam.com</oddFooter>
+    <oddFooter>&amp;CGenerated with ProbeMatrix Learnings Coach v2.0.0a7 (open source, MIT) from a ProbeMatrix four-level human-factors investigation. ProbeMatrix by Eyekyam: ashley@eyekyam.com</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>

--- a/samples/2020-09-24-hazira-gas-release-fire/outputs/nine-m-analysis.actions-template.xlsx
+++ b/samples/2020-09-24-hazira-gas-release-fire/outputs/nine-m-analysis.actions-template.xlsx
@@ -821,7 +821,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter>
     <oddHeader>&amp;CLearning purposes: not a statutory document · DRAFT</oddHeader>
-    <oddFooter>&amp;CGenerated with ProbeMatrix Learnings Coach v2.0.0a7 (open source, MIT) from a ProbeMatrix four-level human-factors investigation. ProbeMatrix by Eyekyam: ashley@eyekyam.com</oddFooter>
+    <oddFooter>&amp;CGenerated with ProbeMatrix Learnings Coach v2.0.0a8 (open source, MIT) from a ProbeMatrix four-level human-factors investigation. ProbeMatrix by Eyekyam: ashley@eyekyam.com</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
